--- a/ControlPad2025/CoordTrans.xlsx
+++ b/ControlPad2025/CoordTrans.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FrcProj\2025\ControlPad2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FrcProj\2025\FRC5515_2025\ControlPad2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB85CEF9-133D-4A13-85A7-D9593CECDA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C8EE49-497F-436F-B475-73829F8A391E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4905" yWindow="4215" windowWidth="27480" windowHeight="17880" xr2:uid="{EF4FB274-D576-4A52-BA7B-AFA7CC462D5C}"/>
+    <workbookView xWindow="8070" yWindow="8865" windowWidth="27480" windowHeight="17880" activeTab="1" xr2:uid="{EF4FB274-D576-4A52-BA7B-AFA7CC462D5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>inches</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,6 +117,18 @@
   </si>
   <si>
     <t>algea位置Y（相对于场中心）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aprilTag17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1112,4 +1125,318 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67886DF6-BD57-4320-86B0-73BE74B65475}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="15.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+      <c r="C2">
+        <v>240</v>
+      </c>
+      <c r="D2">
+        <v>4.0739059999999991</v>
+      </c>
+      <c r="E2">
+        <f>D2 + B2*COS(C2+90)</f>
+        <v>3.5783065891223957</v>
+      </c>
+      <c r="F2">
+        <f>D2 +B2*SIN(C2+90)</f>
+        <v>4.0077151853972728</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>240</v>
+      </c>
+      <c r="D3">
+        <v>3.3063179999999996</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E22" si="0">D3 + B3*COS(C3+90)</f>
+        <v>2.8107185891223962</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F22" si="1">D3 +B3*SIN(C3+90)</f>
+        <v>3.2401271853972737</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>0.5</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>0.5</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>0.5</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>0.5</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>0.5</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>0.5</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>0.5</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>0.5</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>0.5</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>0.5</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>0.5</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>0.5</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>0.5</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>-0.22403680806458506</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>0.44699833180027893</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ControlPad2025/CoordTrans.xlsx
+++ b/ControlPad2025/CoordTrans.xlsx
@@ -1,32 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FrcProj\2025\FRC5515_2025\ControlPad2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C8EE49-497F-436F-B475-73829F8A391E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130F9B6B-2398-4C1E-8E7C-3B6805594625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8070" yWindow="8865" windowWidth="27480" windowHeight="17880" activeTab="1" xr2:uid="{EF4FB274-D576-4A52-BA7B-AFA7CC462D5C}"/>
+    <workbookView xWindow="5085" yWindow="2745" windowWidth="27480" windowHeight="17880" xr2:uid="{EF4FB274-D576-4A52-BA7B-AFA7CC462D5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>inches</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -129,6 +140,30 @@
   </si>
   <si>
     <t>y结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AP6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AP7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AP8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AP9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AP10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AP11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -496,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72287B30-E452-4953-8A63-39D0B9B8F731}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.125" customWidth="1"/>
@@ -553,19 +588,19 @@
         <v>217.25</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C26" si="0">B:B*0.0254</f>
+        <f t="shared" ref="C3:C39" si="0">B:B*0.0254</f>
         <v>5.5181499999999994</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D26" si="1">C:C*937/17.548</f>
+        <f t="shared" ref="D3:D39" si="1">C:C*937/17.548</f>
         <v>294.64933610667879</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E26" si="2">430-D3</f>
+        <f t="shared" ref="E3:E39" si="2">430-D3</f>
         <v>135.35066389332121</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F26" si="3">937-D3</f>
+        <f t="shared" ref="F3:F39" si="3">937-D3</f>
         <v>642.35066389332121</v>
       </c>
     </row>
@@ -1111,8 +1146,308 @@
         <v>839.34866651470247</v>
       </c>
     </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="2"/>
+        <v>430</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>937</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>530.49</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>13.474446</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="1"/>
+        <v>719.48688750854808</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="2"/>
+        <v>-289.48688750854808</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>217.51311249145192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+      <c r="B29">
+        <v>130.16999999999999</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>3.3063179999999996</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="1"/>
+        <v>176.54547333029407</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="2"/>
+        <v>253.45452666970593</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="3"/>
+        <v>760.45452666970596</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>546.87</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>13.890497999999999</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="1"/>
+        <v>741.70256587645326</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="2"/>
+        <v>-311.70256587645326</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="3"/>
+        <v>195.29743412354674</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="1"/>
+      <c r="B31">
+        <v>158.5</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>4.0259</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="1"/>
+        <v>214.96856051971739</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="2"/>
+        <v>215.03143948028261</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="3"/>
+        <v>722.03143948028264</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32">
+        <v>530.49</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>13.474446</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="1"/>
+        <v>719.48688750854808</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="2"/>
+        <v>-289.48688750854808</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="3"/>
+        <v>217.51311249145192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="1"/>
+      <c r="B33">
+        <v>186.83</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>4.745482</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="1"/>
+        <v>253.39164770914064</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="2"/>
+        <v>176.60835229085936</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>683.60835229085933</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34">
+        <v>497.77</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>12.643357999999999</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="1"/>
+        <v>675.10978151356278</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="2"/>
+        <v>-245.10978151356278</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="3"/>
+        <v>261.89021848643722</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="1"/>
+      <c r="B35">
+        <v>186.83</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>4.745482</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="1"/>
+        <v>253.39164770914064</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="2"/>
+        <v>176.60835229085936</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>683.60835229085933</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36">
+        <v>481.39</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>12.227305999999999</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="1"/>
+        <v>652.89410314565771</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="2"/>
+        <v>-222.89410314565771</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="3"/>
+        <v>284.10589685434229</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="1"/>
+      <c r="B37">
+        <v>158.5</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>4.0259</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="1"/>
+        <v>214.96856051971739</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="2"/>
+        <v>215.03143948028261</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="3"/>
+        <v>722.03143948028264</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38">
+        <v>497.77</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>12.643357999999999</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="1"/>
+        <v>675.10978151356278</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="2"/>
+        <v>-245.10978151356278</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="3"/>
+        <v>261.89021848643722</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="1"/>
+      <c r="B39">
+        <v>130.16999999999999</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>3.3063179999999996</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="1"/>
+        <v>176.54547333029407</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="2"/>
+        <v>253.45452666970593</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="3"/>
+        <v>760.45452666970596</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A10:A11"/>
